--- a/data/trans_dic/P64D1_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D1_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,83; 30,33</t>
+          <t>21,35; 31,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,21; 43,37</t>
+          <t>32,48; 42,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,36; 34,49</t>
+          <t>27,46; 34,32</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 25,0</t>
+          <t>21,63; 29,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,44; 45,92</t>
+          <t>37,62; 46,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,24; 32,04</t>
+          <t>29,51; 35,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,18; 22,51</t>
+          <t>13,4; 22,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 28,26</t>
+          <t>24,25; 33,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 23,66</t>
+          <t>19,64; 25,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 32,51</t>
+          <t>24,73; 33,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,87; 69,37</t>
+          <t>36,54; 44,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,74; 52,71</t>
+          <t>31,52; 37,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,95; 24,34</t>
+          <t>22,56; 26,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,38; 48,59</t>
+          <t>35,56; 39,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,33</t>
+          <t>28,84; 31,94</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83889</t>
+          <t>95691</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>104007</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182427</t>
+          <t>199697</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>69391; 101019</t>
+          <t>78335; 115096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85713; 111911</t>
+          <t>90630; 118904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161718; 203874</t>
+          <t>177363; 221656</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>160825</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>166723</t>
+          <t>187914</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298771</t>
+          <t>348739</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57438; 201394</t>
+          <t>135859; 184186</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>150105; 184092</t>
+          <t>168197; 207309</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159756; 386526</t>
+          <t>317240; 380541</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>73583</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>95770</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>169353</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46932; 80131</t>
+          <t>55962; 94705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51847; 91093</t>
+          <t>81874; 112108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110887; 160485</t>
+          <t>148312; 193859</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>131520</t>
+          <t>146980</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>235952</t>
+          <t>182876</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367473</t>
+          <t>329856</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>112082; 153133</t>
+          <t>127783; 173535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>186408; 332674</t>
+          <t>163572; 200315</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311226; 501086</t>
+          <t>304005; 357622</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>274125; 478461</t>
+          <t>435206; 519577</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>516941; 709865</t>
+          <t>537411; 603879</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>808557; 1142099</t>
+          <t>992323; 1098725</t>
         </is>
       </c>
     </row>
